--- a/GUA/IPPU/A1_Inputs/A-I_Horizon_Configuration.xlsx
+++ b/GUA/IPPU/A1_Inputs/A-I_Horizon_Configuration.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clgcr.sharepoint.com/sites/ClimateLeadGroup-Decarb_GU/Documentos compartidos/Decarb_GU/4_Model/2_Residuos&amp;PIUP/modelo_pi_202302/t1_confection/A1_Inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\IPPU_CR_v2\A1_Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{12A48412-8A79-41A4-8D13-3854B5441106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08C675F6-2BB6-4EC0-851D-98BA8AF853F5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BF3E1C-942E-4015-96A0-91AEDF820FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Horizon" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -374,13 +385,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -388,7 +399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>2018</v>
       </c>
@@ -403,6 +414,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
     <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
@@ -625,15 +645,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -645,17 +656,25 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47F89A9F-2BE2-4BCF-997E-BD95B5E485DD}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43DD5183-7D14-410F-B257-3A8F314851EA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB815CDD-081E-435E-8A65-3F13801F858B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB5431B3-EFD7-469A-B718-1E68A2C7F3D0}"/>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59D66996-E179-47E9-8B77-91328ADCB126}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A2AC8F-D36D-463A-B137-1935D135D22C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0d55314f-45f1-40c9-9fce-63556e193d03"/>
+    <ds:schemaRef ds:uri="48eed89a-7418-4977-ae3a-838f0fac8ec5"/>
+    <ds:schemaRef ds:uri="416d42ac-85ec-40c4-8054-6c816fd4b6a7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>